--- a/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0013574371260267372</v>
       </c>
       <c r="B2">
-        <v>0.001607975811747815</v>
+        <v>0.0015276155338870322</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0027148742520534744</v>
       </c>
       <c r="B3">
-        <v>0.0024443340487664612</v>
+        <v>0.0023335671792826793</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0040723113780802116</v>
       </c>
       <c r="B4">
-        <v>0.0031544110392558145</v>
+        <v>0.0030201876562342906</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0054297485041069488</v>
       </c>
       <c r="B5">
-        <v>0.0037743046416885595</v>
+        <v>0.0036211857338727432</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0067871856301336851</v>
       </c>
       <c r="B6">
-        <v>0.0043188575174377252</v>
+        <v>0.00415043075688467</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0081446227561604231</v>
       </c>
       <c r="B7">
-        <v>0.0047966160340070932</v>
+        <v>0.0046159140037904138</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.00950205988218716</v>
       </c>
       <c r="B8">
-        <v>0.0052126779642295337</v>
+        <v>0.0050224073298582167</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.010859497008213898</v>
       </c>
       <c r="B9">
-        <v>0.0055748827633136473</v>
+        <v>0.0053772399177641535</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.012216934134240633</v>
       </c>
       <c r="B10">
-        <v>0.0058916704892655325</v>
+        <v>0.00568830077016147</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.01357437126026737</v>
       </c>
       <c r="B11">
-        <v>0.0061711419289055816</v>
+        <v>0.0059631608422042693</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.014931808386294109</v>
       </c>
       <c r="B12">
-        <v>0.0064176773703499843</v>
+        <v>0.0062059179512596666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.016289245512320846</v>
       </c>
       <c r="B13">
-        <v>0.0066211143780838342</v>
+        <v>0.0064070954110459549</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.017646682638347583</v>
       </c>
       <c r="B14">
-        <v>0.0067754112858090963</v>
+        <v>0.0065610619324642915</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.019004119764374321</v>
       </c>
       <c r="B15">
-        <v>0.00690555222772631</v>
+        <v>0.0066911423187961342</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.020361556890401054</v>
       </c>
       <c r="B16">
-        <v>0.0070344520592161225</v>
+        <v>0.0068187294949192991</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.021718994016427795</v>
       </c>
       <c r="B17">
-        <v>0.0071457227198810395</v>
+        <v>0.0069285327797167619</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.023076431142454532</v>
       </c>
       <c r="B18">
-        <v>0.0072181728161041375</v>
+        <v>0.0070007776858018395</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.024433868268481266</v>
       </c>
       <c r="B19">
-        <v>0.0072507005371689045</v>
+        <v>0.0070344381067040575</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.025791305394508007</v>
       </c>
       <c r="B20">
-        <v>0.007247226468083936</v>
+        <v>0.00703317503118199</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.02714874252053474</v>
       </c>
       <c r="B21">
-        <v>0.007211671193857825</v>
+        <v>0.0070006494479942132</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.028506179646561478</v>
       </c>
       <c r="B22">
-        <v>0.0071472536903481043</v>
+        <v>0.0069398669303281525</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.029863616772588218</v>
       </c>
       <c r="B23">
-        <v>0.0070543864968080731</v>
+        <v>0.00685121138908665</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.031221053898614955</v>
       </c>
       <c r="B24">
-        <v>0.0069327805433399706</v>
+        <v>0.0067344113196014</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.032578491024641693</v>
       </c>
       <c r="B25">
-        <v>0.0067821467600460376</v>
+        <v>0.0065891952172040932</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.033935928150668426</v>
       </c>
       <c r="B26">
-        <v>0.00660207367972825</v>
+        <v>0.0064151767680011686</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.035293365276695167</v>
       </c>
       <c r="B27">
-        <v>0.00639166024598754</v>
+        <v>0.0062115104211980321</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.0366508024027219</v>
       </c>
       <c r="B28">
-        <v>0.0061498830051245762</v>
+        <v>0.0059772358167748379</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.038008239528748641</v>
       </c>
       <c r="B29">
-        <v>0.0058757185034400295</v>
+        <v>0.0057113925947117382</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.039365676654775375</v>
       </c>
       <c r="B30">
-        <v>0.0055686510255779529</v>
+        <v>0.0054134936680032431</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.040723113780802109</v>
       </c>
       <c r="B31">
-        <v>0.0052301958095559223</v>
+        <v>0.00508494504170129</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.042080550906828849</v>
       </c>
       <c r="B32">
-        <v>0.0048623758317348949</v>
+        <v>0.0047276259938721747</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.04343798803285559</v>
       </c>
       <c r="B33">
-        <v>0.00446721406847583</v>
+        <v>0.0043434158025821906</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.044795425158882324</v>
       </c>
       <c r="B34">
-        <v>0.0040458884268750233</v>
+        <v>0.0039334042908321333</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.046152862284909064</v>
       </c>
       <c r="B35">
-        <v>0.0035961965369701223</v>
+        <v>0.0034955234613607915</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.0475102994109358</v>
       </c>
       <c r="B36">
-        <v>0.0031150909595341145</v>
+        <v>0.0030269158618414539</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.048867736536962532</v>
       </c>
       <c r="B37">
-        <v>0.0025995242553399807</v>
+        <v>0.0025247240399474034</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.050225173662989273</v>
       </c>
       <c r="B38">
-        <v>0.0020443912134975534</v>
+        <v>0.0019841692076942754</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.051582610789016013</v>
       </c>
       <c r="B39">
-        <v>0.0014363555364640449</v>
+        <v>0.0013927872344670906</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.052940047915042747</v>
       </c>
       <c r="B40">
-        <v>0.00076002315503351443</v>
+        <v>0.00073619265399321688</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.054297485041069481</v>
       </c>
       <c r="B41">
-        <v>2.411292722873414E-17</v>
+        <v>2.4301309472708626E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.054297485041069481</v>
       </c>
       <c r="B42">
-        <v>2.411292722873414E-17</v>
+        <v>2.4136475009230951E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.052940047915042747</v>
       </c>
       <c r="B43">
-        <v>4.5108123824584425E-05</v>
+        <v>6.89386248648822E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.051582610789016013</v>
       </c>
       <c r="B44">
-        <v>0.0001293064765554229</v>
+        <v>0.00017287477855237708</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.050225173662989273</v>
       </c>
       <c r="B45">
-        <v>0.00023773103939922128</v>
+        <v>0.000297953045202499</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.048867736536962532</v>
       </c>
       <c r="B46">
-        <v>0.0003555177935626614</v>
+        <v>0.00043031800895523869</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.0475102994109358</v>
       </c>
       <c r="B47">
-        <v>0.00046983802875430312</v>
+        <v>0.00055801312644696358</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.046152862284909064</v>
       </c>
       <c r="B48">
-        <v>0.0005760042686902187</v>
+        <v>0.00067667734429954893</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.044795425158882324</v>
       </c>
       <c r="B49">
-        <v>0.00067136434558835972</v>
+        <v>0.00078384848163124874</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.04343798803285559</v>
       </c>
       <c r="B50">
-        <v>0.00075326609166667647</v>
+        <v>0.00087706435756031511</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.042080550906828849</v>
       </c>
       <c r="B51">
-        <v>0.00081988069585328422</v>
+        <v>0.0009546305337160047</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.040723113780802109</v>
       </c>
       <c r="B52">
-        <v>0.000872672773916957</v>
+        <v>0.001017923541771589</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.039365676654775375</v>
       </c>
       <c r="B53">
-        <v>0.000913930298336633</v>
+        <v>0.0010690876559113435</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.038008239528748641</v>
       </c>
       <c r="B54">
-        <v>0.00094594124159125151</v>
+        <v>0.001110267150319544</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.0366508024027219</v>
       </c>
       <c r="B55">
-        <v>0.00097046735463240366</v>
+        <v>0.0011431145429821427</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.035293365276695167</v>
       </c>
       <c r="B56">
-        <v>0.00098716550230229234</v>
+        <v>0.0011673153270918006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.033935928150668426</v>
       </c>
       <c r="B57">
-        <v>0.00099516632791577376</v>
+        <v>0.0011820632396428563</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.032578491024641693</v>
       </c>
       <c r="B58">
-        <v>0.00099360047478770338</v>
+        <v>0.0011865520176296482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.031221053898614955</v>
       </c>
       <c r="B59">
-        <v>0.00098170383118281919</v>
+        <v>0.0011800730549213912</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.029863616772588218</v>
       </c>
       <c r="B60">
-        <v>0.00095913326516538545</v>
+        <v>0.0011623083728868088</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.028506179646561478</v>
       </c>
       <c r="B61">
-        <v>0.0009256508897495481</v>
+        <v>0.0011330376497695</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.02714874252053474</v>
       </c>
       <c r="B62">
-        <v>0.000881018817949453</v>
+        <v>0.0010920405638130658</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.025791305394508007</v>
       </c>
       <c r="B63">
-        <v>0.00082568336102554769</v>
+        <v>0.0010397347979274943</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.024433868268481266</v>
       </c>
       <c r="B64">
-        <v>0.00076282762322348475</v>
+        <v>0.00097909005368833259</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.023076431142454532</v>
       </c>
       <c r="B65">
-        <v>0.00069631890703521833</v>
+        <v>0.00091371403733751593</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.021718994016427795</v>
       </c>
       <c r="B66">
-        <v>0.00063002451495270219</v>
+        <v>0.00084721445511698023</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.020361556890401054</v>
       </c>
       <c r="B67">
-        <v>0.00056277513031143</v>
+        <v>0.00077849769460825325</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.019004119764374321</v>
       </c>
       <c r="B68">
-        <v>0.00047325495982105461</v>
+        <v>0.00068766486875123</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.017646682638347583</v>
       </c>
       <c r="B69">
-        <v>0.0003449306854649788</v>
+        <v>0.00055928003880978286</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.016289245512320846</v>
       </c>
       <c r="B70">
-        <v>0.00020054536694745029</v>
+        <v>0.00041456433398533</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.014931808386294109</v>
       </c>
       <c r="B71">
-        <v>6.4894797640469129E-05</v>
+        <v>0.00027665421673078657</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.01357437126026737</v>
       </c>
       <c r="B72">
-        <v>-6.8290672133793608E-05</v>
+        <v>0.00013969041456751919</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.012216934134240633</v>
       </c>
       <c r="B73">
-        <v>-0.00020942108385635342</v>
+        <v>-6.0513647522903038E-06</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.010859497008213898</v>
       </c>
       <c r="B74">
-        <v>-0.00035440260317114104</v>
+        <v>-0.00015675975762164792</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.00950205988218716</v>
       </c>
       <c r="B75">
-        <v>-0.00049544106690997181</v>
+        <v>-0.00030517043253865475</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0081446227561604231</v>
       </c>
       <c r="B76">
-        <v>-0.00062444487249328426</v>
+        <v>-0.0004437428422766047</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0067871856301336851</v>
       </c>
       <c r="B77">
-        <v>-0.00073394529915394614</v>
+        <v>-0.00056551853860089022</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0054297485041069488</v>
       </c>
       <c r="B78">
-        <v>-0.00081926259278591743</v>
+        <v>-0.00066614368497010137</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0040723113780802116</v>
       </c>
       <c r="B79">
-        <v>-0.00087229045138989807</v>
+        <v>-0.00073806706836837424</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0027148742520534744</v>
       </c>
       <c r="B80">
-        <v>-0.00087867203574699</v>
+        <v>-0.00076790516626320832</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0013574371260267372</v>
       </c>
       <c r="B81">
-        <v>-0.00080283252407566965</v>
+        <v>-0.00072247224621488685</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0015807940883116767</v>
       </c>
       <c r="B2">
-        <v>0.00072306652084400081</v>
+        <v>0.00056163582854561254</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0031615881766233534</v>
       </c>
       <c r="B3">
-        <v>0.0010754146075044547</v>
+        <v>0.00085290203163370325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.00474238226493503</v>
       </c>
       <c r="B4">
-        <v>0.0013700494363242928</v>
+        <v>0.001100416550269147</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0063231763532467069</v>
       </c>
       <c r="B5">
-        <v>0.0016243672460059025</v>
+        <v>0.0013167763323022165</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0079039704415583834</v>
       </c>
       <c r="B6">
-        <v>0.0018454593073193209</v>
+        <v>0.0015071174140177861</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.00948476452987006</v>
       </c>
       <c r="B7">
-        <v>0.0020373723262643779</v>
+        <v>0.0016743714181771915</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.011065558618181738</v>
       </c>
       <c r="B8">
-        <v>0.0022024847378734943</v>
+        <v>0.0018202620645792684</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.012646352706493414</v>
       </c>
       <c r="B9">
-        <v>0.0023445161868522204</v>
+        <v>0.0019474839436318596</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.014227146794805091</v>
       </c>
       <c r="B10">
-        <v>0.0024674828585127466</v>
+        <v>0.0020589462603146538</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.015807940883116767</v>
       </c>
       <c r="B11">
-        <v>0.0025752458909206757</v>
+        <v>0.0021574458072857114</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.017388734971428444</v>
       </c>
       <c r="B12">
-        <v>0.0026698657480484327</v>
+        <v>0.0022444756108505985</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.018969529059740121</v>
       </c>
       <c r="B13">
-        <v>0.0027463552447422948</v>
+        <v>0.0023164260442265325</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0205503231480518</v>
       </c>
       <c r="B14">
-        <v>0.0028017311695368381</v>
+        <v>0.0023711382768130283</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.022131117236363476</v>
       </c>
       <c r="B15">
-        <v>0.0028480738548459679</v>
+        <v>0.0024173593158271327</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.02371191132467515</v>
       </c>
       <c r="B16">
-        <v>0.0028964633227423287</v>
+        <v>0.00246311187317231</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.025292705412986827</v>
       </c>
       <c r="B17">
-        <v>0.0029389148100541877</v>
+        <v>0.0025026156416801649</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.026873499501298505</v>
       </c>
       <c r="B18">
-        <v>0.0029651175727288957</v>
+        <v>0.0025284062108319656</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.028454293589610182</v>
       </c>
       <c r="B19">
-        <v>0.0029745217284345249</v>
+        <v>0.0025400857757794911</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.03003508767792186</v>
       </c>
       <c r="B20">
-        <v>0.0029690176102693251</v>
+        <v>0.0025390231830921496</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.031615881766233533</v>
       </c>
       <c r="B21">
-        <v>0.002950495551331549</v>
+        <v>0.0025265872793393484</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.033196675854545214</v>
       </c>
       <c r="B22">
-        <v>0.0029205093787816171</v>
+        <v>0.0025039032005210182</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.034777469942856888</v>
       </c>
       <c r="B23">
-        <v>0.0028792668960286334</v>
+        <v>0.0024711212403591767</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.036358264031168569</v>
       </c>
       <c r="B24">
-        <v>0.0028266394005438708</v>
+        <v>0.0024281479820063645</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.037939058119480243</v>
       </c>
       <c r="B25">
-        <v>0.0027624981897986039</v>
+        <v>0.0023748900086151222</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.039519852207791917</v>
       </c>
       <c r="B26">
-        <v>0.0026866590521031474</v>
+        <v>0.0023112136373821812</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.0411006462961036</v>
       </c>
       <c r="B27">
-        <v>0.0025987157391239792</v>
+        <v>0.0022368241216810278</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.042681440384415271</v>
       </c>
       <c r="B28">
-        <v>0.0024982064933666177</v>
+        <v>0.0021513864489293411</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.044262234472726952</v>
       </c>
       <c r="B29">
-        <v>0.0023846695573365826</v>
+        <v>0.0020545656065447974</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.045843028561038626</v>
       </c>
       <c r="B30">
-        <v>0.002257893742855426</v>
+        <v>0.0019462079160360345</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.0474238226493503</v>
       </c>
       <c r="B31">
-        <v>0.0021186701390088374</v>
+        <v>0.0018268850352755322</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.049004616737661981</v>
       </c>
       <c r="B32">
-        <v>0.0019680404041985378</v>
+        <v>0.0016973499562267264</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.050585410825973655</v>
       </c>
       <c r="B33">
-        <v>0.0018070461968262503</v>
+        <v>0.0015583556708530571</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.052166204914285336</v>
       </c>
       <c r="B34">
-        <v>0.001636324098543838</v>
+        <v>0.0014103618142241215</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.05374699900259701</v>
       </c>
       <c r="B35">
-        <v>0.0014548903840037304</v>
+        <v>0.0012526545938341537</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.055327793090908683</v>
       </c>
       <c r="B36">
-        <v>0.0012613562511084992</v>
+        <v>0.0010842268602835488</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.056908587179220364</v>
       </c>
       <c r="B37">
-        <v>0.001054332897760712</v>
+        <v>0.00090407146417269865</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.058489381267532038</v>
       </c>
       <c r="B38">
-        <v>0.00083143822127082424</v>
+        <v>0.000710462033193642</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.060070175355843719</v>
       </c>
       <c r="B39">
-        <v>0.000586316916580821</v>
+        <v>0.00049879530340499211</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.061650969444155393</v>
       </c>
       <c r="B40">
-        <v>0.00031162037804057088</v>
+        <v>0.00026374878795700656</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.061650969444155393</v>
       </c>
       <c r="B43">
-        <v>-3.5275202275112137E-05</v>
+        <v>1.2596387808452119E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.060070175355843719</v>
       </c>
       <c r="B44">
-        <v>-4.789767164982257E-05</v>
+        <v>3.9623941526006231E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.058489381267532038</v>
       </c>
       <c r="B45">
-        <v>-4.5200822766728406E-05</v>
+        <v>7.5775365310453842E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.056908587179220364</v>
       </c>
       <c r="B46">
-        <v>-3.451807026837079E-05</v>
+        <v>0.00011574336331964261</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.055327793090908683</v>
       </c>
       <c r="B47">
-        <v>-2.2190059217227346E-05</v>
+        <v>0.00015493933160772285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.05374699900259701</v>
       </c>
       <c r="B48">
-        <v>-1.0586356355521474E-05</v>
+        <v>0.0001916494338140553</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.052166204914285336</v>
       </c>
       <c r="B49">
-        <v>-1.0837588454128932E-06</v>
+        <v>0.00022487852547430374</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.050585410825973655</v>
       </c>
       <c r="B50">
-        <v>4.9409361509385358E-06</v>
+        <v>0.00025363146212413154</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.049004616737661981</v>
       </c>
       <c r="B51">
-        <v>6.5154188955570215E-06</v>
+        <v>0.0002772058668673684</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.0474238226493503</v>
       </c>
       <c r="B52">
-        <v>4.2853293472028416E-06</v>
+        <v>0.00029607043308050836</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.045843028561038626</v>
       </c>
       <c r="B53">
-        <v>-6.9920511117967E-07</v>
+        <v>0.00031098662170821184</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.044262234472726952</v>
       </c>
       <c r="B54">
-        <v>-7.3880570966462572E-06</v>
+        <v>0.00032271589369513922</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.042681440384415271</v>
       </c>
       <c r="B55">
-        <v>-1.4982234439738778E-05</v>
+        <v>0.00033183780999753836</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.0411006462961036</v>
       </c>
       <c r="B56">
-        <v>-2.3687285824943831E-05</v>
+        <v>0.00033820433161800751</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.039519852207791917</v>
       </c>
       <c r="B57">
-        <v>-3.3959895150234229E-05</v>
+        <v>0.00034148551957073251</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.037939058119480243</v>
       </c>
       <c r="B58">
-        <v>-4.6256746313582717E-05</v>
+        <v>0.00034135143486989909</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.036358264031168569</v>
       </c>
       <c r="B59">
-        <v>-6.09795743655979E-05</v>
+        <v>0.00033751184417190878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.034777469942856888</v>
       </c>
       <c r="B60">
-        <v>-7.83103189674312E-05</v>
+        <v>0.00032983533670202564</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.033196675854545214</v>
       </c>
       <c r="B61">
-        <v>-9.8375970932869781E-05</v>
+        <v>0.00031823020732772933</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.031615881766233533</v>
       </c>
       <c r="B62">
-        <v>-0.0001213035210757008</v>
+        <v>0.0003026047509164996</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.03003508767792186</v>
       </c>
       <c r="B63">
-        <v>-0.0001468840359420938</v>
+        <v>0.000283110391235082</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.028454293589610182</v>
       </c>
       <c r="B64">
-        <v>-0.00017356488500774796</v>
+        <v>0.00026087106764728559</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.026873499501298505</v>
       </c>
       <c r="B65">
-        <v>-0.00019945751348074479</v>
+        <v>0.00023725384841618555</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.025292705412986827</v>
       </c>
       <c r="B66">
-        <v>-0.00022267336656916595</v>
+        <v>0.00021362580180485681</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.02371191132467515</v>
       </c>
       <c r="B67">
-        <v>-0.00024376457269259289</v>
+        <v>0.00018958687687742622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.022131117236363476</v>
       </c>
       <c r="B68">
-        <v>-0.00027304599311660726</v>
+        <v>0.000157668545902228</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0205503231480518</v>
       </c>
       <c r="B69">
-        <v>-0.000318507183534245</v>
+        <v>0.00011208570918956442</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.018969529059740121</v>
       </c>
       <c r="B70">
-        <v>-0.00036907374450235775</v>
+        <v>6.0855456013404357E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.017388734971428444</v>
       </c>
       <c r="B71">
-        <v>-0.0004126714780228286</v>
+        <v>1.2718659175005493E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.015807940883116767</v>
       </c>
       <c r="B72">
-        <v>-0.00045229094701384744</v>
+        <v>-3.44908633788833E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.014227146794805091</v>
       </c>
       <c r="B73">
-        <v>-0.00049292727335748562</v>
+        <v>-8.4390675159393776E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.012646352706493414</v>
       </c>
       <c r="B74">
-        <v>-0.00053252905387503162</v>
+        <v>-0.00013549681065467086</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.011065558618181738</v>
       </c>
       <c r="B75">
-        <v>-0.00056724477875133214</v>
+        <v>-0.00018502210545710617</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.00948476452987006</v>
       </c>
       <c r="B76">
-        <v>-0.00059306903668625191</v>
+        <v>-0.00023006812859906496</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0079039704415583834</v>
       </c>
       <c r="B77">
-        <v>-0.00060629354269180191</v>
+        <v>-0.00026795164939026687</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0063231763532467069</v>
       </c>
       <c r="B78">
-        <v>-0.00060455241851356133</v>
+        <v>-0.00029696150480987521</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.00474238226493503</v>
       </c>
       <c r="B79">
-        <v>-0.00058381205682893963</v>
+        <v>-0.00031417917077379364</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0031615881766233534</v>
       </c>
       <c r="B80">
-        <v>-0.00053699536257345516</v>
+        <v>-0.00031448278670270368</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0015807940883116767</v>
       </c>
       <c r="B81">
-        <v>-0.00044672110450663991</v>
+        <v>-0.00028529041220825153</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>6.3528057498051288E-05</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0017646682638347584</v>
       </c>
       <c r="B2">
-        <v>0.0004542349963095117</v>
+        <v>0.00019074240063323737</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0035293365276695167</v>
       </c>
       <c r="B3">
-        <v>0.000661738026944155</v>
+        <v>0.00030809850687166956</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0052940047915042759</v>
       </c>
       <c r="B4">
-        <v>0.00083215226841719012</v>
+        <v>0.0004183651764633515</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0070586730553390334</v>
       </c>
       <c r="B5">
-        <v>0.00097712508615828571</v>
+        <v>0.00052431120965828679</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0088233413191737917</v>
       </c>
       <c r="B6">
-        <v>0.0011014019238615941</v>
+        <v>0.00062752534686155747</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.010588009583008552</v>
       </c>
       <c r="B7">
-        <v>0.0012076893260837484</v>
+        <v>0.00072487608909855878</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.01235267784684331</v>
       </c>
       <c r="B8">
-        <v>0.0012975766069697596</v>
+        <v>0.00081306624991671263</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.014117346110678067</v>
       </c>
       <c r="B9">
-        <v>0.0013735517673998257</v>
+        <v>0.00089285613233123736</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.015882014374512827</v>
       </c>
       <c r="B10">
-        <v>0.0014383016030302832</v>
+        <v>0.00096573424514066709</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.017646682638347583</v>
       </c>
       <c r="B11">
-        <v>0.0014944094018868278</v>
+        <v>0.0010320444308090054</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.019411350902182344</v>
       </c>
       <c r="B12">
-        <v>0.001543252546593005</v>
+        <v>0.0010918443652166226</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.021176019166017104</v>
       </c>
       <c r="B13">
-        <v>0.0015814883057943948</v>
+        <v>0.0011451917242438889</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.02294068742985186</v>
       </c>
       <c r="B14">
-        <v>0.0016071163651012095</v>
+        <v>0.0011921480379560952</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.02470535569368662</v>
       </c>
       <c r="B15">
-        <v>0.0016282261919601509</v>
+        <v>0.0012327902531582106</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.026470023957521377</v>
       </c>
       <c r="B16">
-        <v>0.0016522374077520663</v>
+        <v>0.0012671991708401236</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.028234692221356134</v>
       </c>
       <c r="B17">
-        <v>0.001673800467757896</v>
+        <v>0.0012954555919917237</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.029999360485190894</v>
       </c>
       <c r="B18">
-        <v>0.001686008108158522</v>
+        <v>0.0013176076773465002</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.031764028749025654</v>
       </c>
       <c r="B19">
-        <v>0.0016884913548345026</v>
+        <v>0.0013335730266123471</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.03352869701286041</v>
       </c>
       <c r="B20">
-        <v>0.0016825158060913155</v>
+        <v>0.0013432365992407591</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.035293365276695167</v>
       </c>
       <c r="B21">
-        <v>0.0016693470602344382</v>
+        <v>0.001346483354683231</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.037058033540529924</v>
       </c>
       <c r="B22">
-        <v>0.0016500255000854722</v>
+        <v>0.0013432365992407591</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.038822701804364687</v>
       </c>
       <c r="B23">
-        <v>0.0016246906465305156</v>
+        <v>0.0013335730266123471</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.040587370068199444</v>
       </c>
       <c r="B24">
-        <v>0.001593256804971791</v>
+        <v>0.0013176076773465002</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.042352038332034207</v>
       </c>
       <c r="B25">
-        <v>0.0015556382808115203</v>
+        <v>0.0012954555919917237</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.044116706595868957</v>
       </c>
       <c r="B26">
-        <v>0.0015117123666446722</v>
+        <v>0.0012671991708401236</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.04588137485970372</v>
       </c>
       <c r="B27">
-        <v>0.0014612083038371979</v>
+        <v>0.0012327902531582104</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.047646043123538477</v>
       </c>
       <c r="B28">
-        <v>0.0014038183209477944</v>
+        <v>0.0011921480379560949</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.049410711387373241</v>
       </c>
       <c r="B29">
-        <v>0.0013392346465351589</v>
+        <v>0.0011451917242438887</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.051175379651208</v>
       </c>
       <c r="B30">
-        <v>0.0012673175066072275</v>
+        <v>0.0010918443652166222</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.052940047915042754</v>
       </c>
       <c r="B31">
-        <v>0.0011885991169688927</v>
+        <v>0.0010320444308090054</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.05470471617887751</v>
       </c>
       <c r="B32">
-        <v>0.0011037796908742849</v>
+        <v>0.00096573424514066731</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.056469384442712267</v>
       </c>
       <c r="B33">
-        <v>0.001013559441577535</v>
+        <v>0.00089285613233123736</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.058234052706547031</v>
       </c>
       <c r="B34">
-        <v>0.00091836744144438735</v>
+        <v>0.00081306624991671242</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.059998720970381787</v>
       </c>
       <c r="B35">
-        <v>0.00081754819928704051</v>
+        <v>0.00072487608909855823</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.061763389234216544</v>
       </c>
       <c r="B36">
-        <v>0.000710175083029307</v>
+        <v>0.00062752534686155747</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.063528057498051307</v>
       </c>
       <c r="B37">
-        <v>0.00059532146059499758</v>
+        <v>0.00052431120965828679</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.065292725761886064</v>
       </c>
       <c r="B38">
-        <v>0.000471395555102171</v>
+        <v>0.00041836517646335123</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.067057394025720821</v>
       </c>
       <c r="B39">
-        <v>0.00033414501044586986</v>
+        <v>0.000308098506871669</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.068822062289555577</v>
       </c>
       <c r="B40">
-        <v>0.000178652325715383</v>
+        <v>0.00019074240063323667</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.070586730553390334</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>6.3528057498051288E-05</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.070586730553390334</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-6.3528057498051288E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.068822062289555577</v>
       </c>
       <c r="B43">
-        <v>-5.3695059427519275E-05</v>
+        <v>-6.578514283163013E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.067057394025720821</v>
       </c>
       <c r="B44">
-        <v>-9.0645934024432325E-05</v>
+        <v>-6.45994304502314E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.065292725761886064</v>
       </c>
       <c r="B45">
-        <v>-0.00011576900147978699</v>
+        <v>-6.2738614354709962E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.063528057498051307</v>
       </c>
       <c r="B46">
-        <v>-0.00013398063948263141</v>
+        <v>-6.2970388545920673E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.061763389234216544</v>
       </c>
       <c r="B47">
-        <v>-0.000149532119474132</v>
+        <v>-6.68824154936842E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.059998720970381787</v>
       </c>
       <c r="B48">
-        <v>-0.00016401428790392827</v>
+        <v>-7.13422315436843E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.058234052706547031</v>
       </c>
       <c r="B49">
-        <v>-0.00017835288497377826</v>
+        <v>-7.3051727939339262E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.056469384442712267</v>
       </c>
       <c r="B50">
-        <v>-0.00019347365088543981</v>
+        <v>-7.2770341639142292E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.05470471617887751</v>
       </c>
       <c r="B51">
-        <v>-0.00021003122828723854</v>
+        <v>-7.1985764843626417E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.052940047915042754</v>
       </c>
       <c r="B52">
-        <v>-0.000227595869613771</v>
+        <v>-7.1041165006409089E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.051175379651208</v>
       </c>
       <c r="B53">
-        <v>-0.00024546672974620152</v>
+        <v>-6.999357839437892E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.049410711387373241</v>
       </c>
       <c r="B54">
-        <v>-0.00026294296356569452</v>
+        <v>-6.8900041274424465E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.047646043123538477</v>
       </c>
       <c r="B55">
-        <v>-0.00027949176546216206</v>
+        <v>-6.7821487726317192E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.04588137485970372</v>
       </c>
       <c r="B56">
-        <v>-0.00029525248786050771</v>
+        <v>-6.6834443081360262E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.044116706595868957</v>
       </c>
       <c r="B57">
-        <v>-0.0003105325226943827</v>
+        <v>-6.60193304837397E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.042352038332034207</v>
       </c>
       <c r="B58">
-        <v>-0.00032563926189743843</v>
+        <v>-6.5456573077641566E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.040587370068199444</v>
       </c>
       <c r="B59">
-        <v>-0.00034084312647928371</v>
+        <v>-6.5193995540570375E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.038822701804364687</v>
       </c>
       <c r="B60">
-        <v>-0.00035626665375335825</v>
+        <v>-6.5149028683304425E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.037058033540529924</v>
       </c>
       <c r="B61">
-        <v>-0.00037199541010905887</v>
+        <v>-6.5206504849940538E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.035293365276695167</v>
       </c>
       <c r="B62">
-        <v>-0.00038811496193578288</v>
+        <v>-6.5251256384575519E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.03352869701286041</v>
       </c>
       <c r="B63">
-        <v>-0.00040448570370266103</v>
+        <v>-6.5206504849940538E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.031764028749025654</v>
       </c>
       <c r="B64">
-        <v>-0.00042006734219775916</v>
+        <v>-6.5149028683304425E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.029999360485190894</v>
       </c>
       <c r="B65">
-        <v>-0.00043359441228887696</v>
+        <v>-6.5193995540570361E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.028234692221356134</v>
       </c>
       <c r="B66">
-        <v>-0.00044380144884381391</v>
+        <v>-6.5456573077641566E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.026470023957521377</v>
       </c>
       <c r="B67">
-        <v>-0.00045105759414195882</v>
+        <v>-6.60193304837397E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.02470535569368662</v>
       </c>
       <c r="B68">
-        <v>-0.00046227042010905738</v>
+        <v>-6.6834443081360262E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.02294068742985186</v>
       </c>
       <c r="B69">
-        <v>-0.00048278983001062893</v>
+        <v>-6.7821487726317192E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.021176019166017104</v>
       </c>
       <c r="B70">
-        <v>-0.00050519662282493</v>
+        <v>-6.8900041274424451E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.019411350902182344</v>
       </c>
       <c r="B71">
-        <v>-0.00052140178953758777</v>
+        <v>-6.999357839437892E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.017646682638347583</v>
       </c>
       <c r="B72">
-        <v>-0.00053340619345096949</v>
+        <v>-7.1041165006409089E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.015882014374512827</v>
       </c>
       <c r="B73">
-        <v>-0.00054455315823433007</v>
+        <v>-7.1985764843626417E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.014117346110678067</v>
       </c>
       <c r="B74">
-        <v>-0.00055346597670773048</v>
+        <v>-7.2770341639142292E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.01235267784684331</v>
       </c>
       <c r="B75">
-        <v>-0.00055756207815058</v>
+        <v>-7.3051727939339289E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.010588009583008552</v>
       </c>
       <c r="B76">
-        <v>-0.0005541554685288742</v>
+        <v>-7.1342231543684314E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0088233413191737917</v>
       </c>
       <c r="B77">
-        <v>-0.00054075899153069936</v>
+        <v>-6.68824154936842E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0070586730553390334</v>
       </c>
       <c r="B78">
-        <v>-0.0005157842650459196</v>
+        <v>-6.2970388545920673E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0052940047915042759</v>
       </c>
       <c r="B79">
-        <v>-0.00047652571604266662</v>
+        <v>-6.2738614354709949E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0035293365276695167</v>
       </c>
       <c r="B80">
-        <v>-0.00041823895052271688</v>
+        <v>-6.45994304502314E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0017646682638347584</v>
       </c>
       <c r="B81">
-        <v>-0.00032927771283312093</v>
+        <v>-6.578514283163013E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>-6.3528057498051288E-05</v>
       </c>
     </row>
   </sheetData>
